--- a/p6_deployment/data/spain/data_understanding/df_match_next.xlsx
+++ b/p6_deployment/data/spain/data_understanding/df_match_next.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,179 +413,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R2"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>venue</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>capacity</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>attendance</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>id_team_home</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>team_home</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>id_team_away</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>team_away</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>coach_home</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>id_country</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>id_competition</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>is_cup</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>season</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>bDmOFmNG</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>26.05.2024 16:00</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Villanueva J. I. (Esp)</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Estadio Ramón Sánchez Pizjuán (Sevilla)</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>42 714</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>h8oAv4Ts</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Sevilla</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>SKbpVP5K</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Barcelona</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>AD5WKzFn</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>flores quique</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>bs5KnIiT</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>xavi</t>
-        </is>
-      </c>
-      <c r="O2" t="n">
-        <v>148</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1481</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>2023_2024</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/p6_deployment/data/spain/data_understanding/df_match_next.xlsx
+++ b/p6_deployment/data/spain/data_understanding/df_match_next.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,9 +425,639 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:P9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>capacity</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>attendance</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>id_team_home</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>team_home</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>id_team_away</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>team_away</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>id_country</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>id_competition</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>is_cup</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>season</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>competition</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>hO0nKEm3</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>15.08.2024 14:00</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Estadio San Mamés
+ (Bilbao)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>53 331</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>IP5zl0cJ</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Ath Bilbao</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>dboeiWOt</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Getafe</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>148</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>QyafIhIF</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>15.08.2024 16:30</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Estadio Benito Villamarín
+ (Sevilla)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>60 721</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Betis</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>nNNpcUSL</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Girona</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>148</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>nDzACNof</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>16.08.2024 14:00</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Estadio de Balaídos
+ (Vigo)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>24 791</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>8pvUZFhf</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Celta Vigo</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Alaves</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>148</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>hnqZAAAk</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>16.08.2024 16:30</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Estadio de Gran Canaria
+ (Las Palmas)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>32 392</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>IyRQC2vM</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Las Palmas</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>148</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>ruUIA1G6</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>17.08.2024 14:00</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Estadio El Sadar
+ (Pamplona)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>23 516</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>ETdxjU8a</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Osasuna</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Leganes</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>148</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>KbKTWiX8</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>17.08.2024 16:30</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Estadio de Mestalla
+ (Valencia)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>49 430</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>CQeaytrD</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Valencia</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>148</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Eax2EqHs</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>18.08.2024 14:00</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Reale Arena
+ (San Sebastian)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>40 000</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>jNvak2f3</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Real Sociedad</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>8bcjFy6O</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Rayo Vallecano</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>148</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>M3h3GWnS</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>18.08.2024 16:30</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Estadi Mallorca Son Moix
+ (Palma de Mallorca)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>26 020</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>4jDQxrbf</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Mallorca</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Real Madrid</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>148</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/p6_deployment/data/spain/data_understanding/df_match_next.xlsx
+++ b/p6_deployment/data/spain/data_understanding/df_match_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P9"/>
+  <dimension ref="A1:P13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1054,6 +1054,264 @@
       <c r="P9" t="inlineStr">
         <is>
           <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>ITdtTrn2</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>19.08.2024 14:00</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Estadio José Zorrilla
+ (Valladolid)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>27 618</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>zkpajjvm</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Valladolid</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>QFfPdh1J</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Espanyol</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>148</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>E1Xs9lu2</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>19.08.2024 16:30</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Estadio de la Ceramica
+ (Villarreal)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>23 000</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>lUatW5jE</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Villarreal</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>jaarqpLQ</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Atl. Madrid</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>148</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1481</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>LaLiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>ng6idLW1</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>08.01.2025 16:00</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>IP5zl0cJ</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Ath Bilbao</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>148</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1484</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Super Cup</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>CWcwKOO8</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>08.01.2025 16:00</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Real Madrid</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>4jDQxrbf</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Mallorca</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>148</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1484</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Super Cup</t>
         </is>
       </c>
     </row>
